--- a/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
+++ b/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R903ad27fc04b4ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Data" sheetId="2" r:id="R6bb68b25802d4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Calculations" sheetId="3" r:id="Rdccf8defc7e44f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuPont &amp; Driver" sheetId="4" r:id="R0ead31e6db134903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Dashboard" sheetId="5" r:id="R4392ec53e389462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Recommendation" sheetId="6" r:id="Rbd55cd01fcba4ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="7" r:id="Read5c1be8a854d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R21b5ceddb101428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Data" sheetId="2" r:id="Rfaa76ee0da3545dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Calculations" sheetId="3" r:id="R5c75078c7551405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuPont &amp; Driver" sheetId="4" r:id="R8fee8ed6ebd84027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Dashboard" sheetId="5" r:id="R01b9735ffe2d4dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Recommendation" sheetId="6" r:id="Ra86f998e0ae84e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="7" r:id="Rde0ee913d44d41f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Practice" sheetId="8" r:id="Rfed5955485f74439"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,13 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0);-"/>
     <x:numFmt numFmtId="201" formatCode="0.0%;[Red](0.0%);-"/>
     <x:numFmt numFmtId="202" formatCode="0.00x;[Red](0.00x);-"/>
     <x:numFmt numFmtId="203" formatCode="0.00%;[Red](0.00%);-"/>
+    <x:numFmt numFmtId="204" formatCode="0.00&quot;x&quot;"/>
+    <x:numFmt numFmtId="205" formatCode="$#,##0"/>
+    <x:numFmt numFmtId="206" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -86,8 +90,28 @@
       <x:color rgb="FF008000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -142,6 +166,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDCA94A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF192640"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE8F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -268,7 +312,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="235">
+  <x:cellXfs count="257">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -782,6 +826,46 @@
     <x:xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -793,7 +877,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -804,7 +888,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -815,7 +899,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -826,7 +910,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -837,7 +921,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -848,7 +932,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -1067,9 +1151,9 @@
         <x:v>BUS311 | Ratio Analysis and Corporate Performance</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
+    <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>M04 Practice workbook: consistent inputs → ratio families → DuPont and driver evidence → linked dashboard → recommendation.</x:v>
+        <x:v>M04: Class Practice follows the slides. After class, compare two retailers using eight core ratios, DuPont, and one operating test.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
@@ -1077,9 +1161,9 @@
         <x:v>Purpose and deliverable</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>Calculate 14 ratios for each of two firms (28 formulas), reconcile ROE through three-step DuPont analysis, test one operating driver, and defend a concise recommendation against the comparison benchmark.</x:v>
+        <x:v>In class: five ratios and a short brief on Class Practice. After class: eight core ratios per firm (16 formulas), an expense test, and a 4–6 sentence recommendation. Optional ratios are reference only.</x:v>
       </x:c>
       <x:c r="B5" s="15"/>
       <x:c r="C5" s="15"/>
@@ -1115,70 +1199,70 @@
         <x:v>Visible checkpoint</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="39" customHeight="1">
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>Confirm the units, periods, and debt definition in Company Data.</x:v>
+        <x:v>Start with Class Practice during slides 7–12.</x:v>
       </x:c>
       <x:c r="C10" s="32" t="str">
-        <x:v>Current and prior-year denominators are aligned.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="39" customHeight="1">
+        <x:v>Use the same $120,000-revenue example as the deck.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>Enter formulas in the 28 yellow cells on Student Calculations.</x:v>
+        <x:v>After class, use Company Data and Student Calculations.</x:v>
       </x:c>
       <x:c r="C11" s="32" t="str">
-        <x:v>Every ratio references Company Data; no typed answers.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="39" customHeight="1">
+        <x:v>Complete the eight CORE rows for both retailers.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>Use DuPont &amp; Driver to explain ROE through margin, asset use, and leverage.</x:v>
+        <x:v>Read DuPont &amp; Driver after entering the core formulas.</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>DuPont ROE reconciles to direct ROE.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="39" customHeight="1">
+        <x:v>Reconcile ROE and explain the three drivers.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>Enter one operating-expense reduction assumption.</x:v>
+        <x:v>Enter an expense-reduction assumption in DuPont &amp; Driver!B20.</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Scenario ROE and the change from base case calculate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="39" customHeight="1">
+        <x:v>Interpret the effect in B29; use a plausible percentage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>Read the formula-linked dashboard; do not re-enter values there.</x:v>
+        <x:v>Read the linked Ratio Dashboard.</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>All four ratio families and driver evidence update.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="39" customHeight="1">
+        <x:v>Compare drivers, coverage, and illustrative references.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="44" customHeight="1">
       <x:c r="A15" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="34" t="str">
-        <x:v>Review model checks and write the recommendation.</x:v>
+        <x:v>Review Checks &amp; Recommendation and write your response.</x:v>
       </x:c>
       <x:c r="C15" s="35" t="str">
-        <x:v>Status is PASS and the response cites drivers, risk, and a monitoring trigger.</x:v>
+        <x:v>Complete core work and explain one monitoring trigger.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
@@ -1264,13 +1348,13 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
-      <x:c r="A29" s="10" t="str">
-        <x:v>How this differs from the Lemonade Stand activity</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+      <x:c r="A29" s="235" t="str">
+        <x:v>Lemonade Stand is deferred; it is not part of the M04 submission.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="46" customHeight="1">
       <x:c r="A30" s="60" t="str">
-        <x:v>This workbook is a cross-sectional diagnostic: consistent ratio definitions, DuPont drivers, one focused expense test, and a recommendation. The Lemonade Stand activity remains the integrated financing, forecasting, cash-flow, valuation, and dilution application.</x:v>
+        <x:v>Use supplied fictional case data; no FactSet retrieval is required. Complete core comparison work after class. Optional ratios provide definitions for later practice.</x:v>
       </x:c>
       <x:c r="B30" s="61"/>
       <x:c r="C30" s="61"/>
@@ -1326,9 +1410,9 @@
       <x:c r="B1" s="107"/>
       <x:c r="C1" s="107"/>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
+    <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Given classroom-case inputs in USD. Use the current-year income statement with current/prior year-end balance-sheet averages.</x:v>
+        <x:v>Fictional retail cases in USD. Supplied current-year income statements and current/prior year-end balances; no FactSet lookup required.</x:v>
       </x:c>
       <x:c r="B2" s="107"/>
       <x:c r="C2" s="107"/>
@@ -1758,10 +1842,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="39" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1770,12 +1854,12 @@
         <x:v>Student Calculations | Ratio Families</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
+    <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Enter formulas only in yellow cells. Use cell references to Company Data; do not type calculated answers.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="34" customHeight="1">
+        <x:v>After class: enter formulas in yellow CORE rows for both firms. Optional rows may remain blank. All references are illustrative classroom assumptions, not industry targets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="28" t="str">
         <x:v>Ratio</x:v>
       </x:c>
@@ -1783,10 +1867,10 @@
         <x:v>TechStyle Retail</x:v>
       </x:c>
       <x:c r="C4" s="87" t="str">
-        <x:v>Urban Goods</x:v>
+        <x:v>Urban</x:v>
       </x:c>
       <x:c r="D4" s="150" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>Reference (illustrative)</x:v>
       </x:c>
       <x:c r="E4" s="151" t="str">
         <x:v>Definition / denominator contract</x:v>
@@ -1803,7 +1887,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="118" t="str">
-        <x:v>Current Ratio</x:v>
+        <x:v>CORE · Current Ratio</x:v>
       </x:c>
       <x:c r="B6" s="152"/>
       <x:c r="C6" s="152"/>
@@ -1816,10 +1900,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="118" t="str">
-        <x:v>Quick Ratio</x:v>
-      </x:c>
-      <x:c r="B7" s="152"/>
-      <x:c r="C7" s="152"/>
+        <x:v>Optional · Quick Ratio</x:v>
+      </x:c>
+      <x:c r="B7" s="236"/>
+      <x:c r="C7" s="236"/>
       <x:c r="D7" s="153" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1829,10 +1913,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="118" t="str">
-        <x:v>Cash Ratio</x:v>
-      </x:c>
-      <x:c r="B8" s="152"/>
-      <x:c r="C8" s="152"/>
+        <x:v>Optional · Cash Ratio</x:v>
+      </x:c>
+      <x:c r="B8" s="236"/>
+      <x:c r="C8" s="236"/>
       <x:c r="D8" s="153" t="n">
         <x:v>0.5</x:v>
       </x:c>
@@ -1851,7 +1935,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="118" t="str">
-        <x:v>Gross Margin</x:v>
+        <x:v>CORE · Gross Margin</x:v>
       </x:c>
       <x:c r="B10" s="154"/>
       <x:c r="C10" s="154"/>
@@ -1864,10 +1948,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="118" t="str">
-        <x:v>Operating Margin</x:v>
-      </x:c>
-      <x:c r="B11" s="154"/>
-      <x:c r="C11" s="154"/>
+        <x:v>Optional · Operating Margin</x:v>
+      </x:c>
+      <x:c r="B11" s="237"/>
+      <x:c r="C11" s="237"/>
       <x:c r="D11" s="155" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -1877,7 +1961,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="118" t="str">
-        <x:v>Net Profit Margin</x:v>
+        <x:v>CORE · Net Profit Margin</x:v>
       </x:c>
       <x:c r="B12" s="154"/>
       <x:c r="C12" s="154"/>
@@ -1890,10 +1974,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="118" t="str">
-        <x:v>Return on Assets (ROA)</x:v>
-      </x:c>
-      <x:c r="B13" s="154"/>
-      <x:c r="C13" s="154"/>
+        <x:v>Optional · Return on Assets (ROA)</x:v>
+      </x:c>
+      <x:c r="B13" s="237"/>
+      <x:c r="C13" s="237"/>
       <x:c r="D13" s="155" t="n">
         <x:v>0.09</x:v>
       </x:c>
@@ -1903,7 +1987,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="118" t="str">
-        <x:v>Return on Equity (ROE)</x:v>
+        <x:v>CORE · Return on Equity (ROE)</x:v>
       </x:c>
       <x:c r="B14" s="154"/>
       <x:c r="C14" s="154"/>
@@ -1925,10 +2009,10 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="118" t="str">
-        <x:v>Debt-to-Equity</x:v>
-      </x:c>
-      <x:c r="B16" s="152"/>
-      <x:c r="C16" s="152"/>
+        <x:v>Optional · Debt-to-Equity</x:v>
+      </x:c>
+      <x:c r="B16" s="236"/>
+      <x:c r="C16" s="236"/>
       <x:c r="D16" s="153" t="n">
         <x:v>0.8</x:v>
       </x:c>
@@ -1938,7 +2022,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="118" t="str">
-        <x:v>Debt Ratio</x:v>
+        <x:v>CORE · Debt Ratio</x:v>
       </x:c>
       <x:c r="B17" s="154"/>
       <x:c r="C17" s="154"/>
@@ -1951,7 +2035,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="118" t="str">
-        <x:v>Average Equity Multiplier</x:v>
+        <x:v>CORE · Average Equity Multiplier</x:v>
       </x:c>
       <x:c r="B18" s="152"/>
       <x:c r="C18" s="152"/>
@@ -1973,10 +2057,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="118" t="str">
-        <x:v>Inventory Turnover</x:v>
-      </x:c>
-      <x:c r="B20" s="152"/>
-      <x:c r="C20" s="152"/>
+        <x:v>Optional · Inventory Turnover</x:v>
+      </x:c>
+      <x:c r="B20" s="236"/>
+      <x:c r="C20" s="236"/>
       <x:c r="D20" s="153" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1986,10 +2070,10 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="118" t="str">
-        <x:v>Receivables Turnover</x:v>
-      </x:c>
-      <x:c r="B21" s="152"/>
-      <x:c r="C21" s="152"/>
+        <x:v>Optional · Receivables Turnover</x:v>
+      </x:c>
+      <x:c r="B21" s="236"/>
+      <x:c r="C21" s="236"/>
       <x:c r="D21" s="153" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -1999,7 +2083,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="132" t="str">
-        <x:v>Asset Turnover</x:v>
+        <x:v>CORE · Asset Turnover</x:v>
       </x:c>
       <x:c r="B22" s="156"/>
       <x:c r="C22" s="156"/>
@@ -2011,15 +2095,21 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="107"/>
-      <x:c r="B23" s="107"/>
-      <x:c r="C23" s="107"/>
-      <x:c r="D23" s="107"/>
-      <x:c r="E23" s="107"/>
-    </x:row>
-    <x:row r="24" ht="32" customHeight="1">
+      <x:c r="A23" s="107" t="str">
+        <x:v>CORE · Interest coverage</x:v>
+      </x:c>
+      <x:c r="B23" s="239"/>
+      <x:c r="C23" s="239"/>
+      <x:c r="D23" s="238" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="107" t="str">
+        <x:v>EBIT / Interest Expense (same annual period)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="46" customHeight="1">
       <x:c r="A24" s="159" t="str">
-        <x:v>Before moving on: use average denominators for ROA, ROE, turnover ratios, and the DuPont equity multiplier. Use short-term debt + long-term debt for both debt ratios.</x:v>
+        <x:v>Reference values are illustrative, not measured peer averages. Coverage 1.00x is the arithmetic break-even point for EBIT versus interest, not a safe target.</x:v>
       </x:c>
       <x:c r="B24" s="160"/>
       <x:c r="C24" s="160"/>
@@ -2241,7 +2331,7 @@
         <x:v>Model logic</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="91" t="str">
         <x:v>Operating expense reduction (% of revenue)</x:v>
       </x:c>
@@ -2250,7 +2340,7 @@
         <x:f>IF(B20="","",B20)</x:f>
       </x:c>
       <x:c r="D20" s="70" t="str">
-        <x:v>One student-selected assumption applied to both firms</x:v>
+        <x:v>Enter 1% for a reduction equal to 1% of revenue; this is not a 1% cut to existing operating expenses.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2386,6 +2476,12 @@
     <x:mergeCell ref="A18:D18"/>
     <x:mergeCell ref="B29:C29"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="decimal" operator="between" sqref="B20">
+      <x:formula1>0</x:formula1>
+      <x:formula2>0.1</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2410,9 +2506,9 @@
         <x:v>Formula-Linked Ratio Dashboard</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
+    <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Outputs update from Student Calculations. Do not type or paste ratio values on this sheet.</x:v>
+        <x:v>Linked outputs: CORE ratios are required. Blank optional ratios are expected. Reference values are illustrative classroom assumptions.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
@@ -2434,7 +2530,7 @@
         <x:v>Urban</x:v>
       </x:c>
       <x:c r="D5" s="30" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>Illustrative</x:v>
       </x:c>
       <x:c r="F5" s="28" t="str">
         <x:v>Metric</x:v>
@@ -2446,7 +2542,7 @@
         <x:v>Urban</x:v>
       </x:c>
       <x:c r="I5" s="30" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>Illustrative</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2582,7 +2678,7 @@
         <x:v>Urban</x:v>
       </x:c>
       <x:c r="D13" s="30" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>Illustrative</x:v>
       </x:c>
       <x:c r="F13" s="28" t="str">
         <x:v>Metric</x:v>
@@ -2594,7 +2690,7 @@
         <x:v>Urban</x:v>
       </x:c>
       <x:c r="I13" s="30" t="str">
-        <x:v>Benchmark</x:v>
+        <x:v>Illustrative</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2679,6 +2775,21 @@
       <x:c r="I16" s="185" t="n">
         <x:f>IF('Student Calculations'!D22="","",'Student Calculations'!D22)</x:f>
         <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Interest coverage</x:v>
+      </x:c>
+      <x:c r="B17" s="240" t="str">
+        <x:f>IF('Student Calculations'!B23="","",'Student Calculations'!B23)</x:f>
+      </x:c>
+      <x:c r="C17" s="240" t="str">
+        <x:f>IF('Student Calculations'!C23="","",'Student Calculations'!C23)</x:f>
+      </x:c>
+      <x:c r="D17" s="240" t="n">
+        <x:f>IF('Student Calculations'!D23="","",'Student Calculations'!D23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
@@ -2873,7 +2984,7 @@
         <x:v>MODEL STATUS</x:v>
       </x:c>
       <x:c r="B4" s="211" t="str">
-        <x:f>IF(COUNTIF(G7:G14,"REVIEW")&gt;0,"REVIEW",IF(COUNTIF(G7:G14,"WAITING")&gt;0,"WAITING","PASS"))</x:f>
+        <x:f>IFERROR(IF(COUNTIF(G8:G15,"REVIEW")&gt;0,"REVIEW",IF(OR(COUNT('Student Calculations'!B6:C6,'Student Calculations'!B10:C10,'Student Calculations'!B12:C12,'Student Calculations'!B14:C14,'Student Calculations'!B17:C17,'Student Calculations'!B18:C18,'Student Calculations'!B22:C22,'Student Calculations'!B23:C23)&lt;16,COUNTIF(G8:G15,"WAITING")&gt;0,'DuPont &amp; Driver'!B20="",'DuPont &amp; Driver'!B29="",A19=""),"WAITING","PASS")),"REVIEW")</x:f>
         <x:v>WAITING</x:v>
       </x:c>
       <x:c r="C4" s="211"/>
@@ -3050,8 +3161,8 @@
         <x:v>0.0001</x:v>
       </x:c>
       <x:c r="G12" s="48" t="str">
-        <x:f>IF(COUNT(C12:D12)&lt;2,"WAITING",IF(ABS(E12)&lt;=F12,"PASS","REVIEW"))</x:f>
-        <x:v>WAITING</x:v>
+        <x:f>IF('Student Calculations'!B13="","OPTIONAL",IF(COUNT(C12:D12)&lt;2,"WAITING",IF(ABS(E12)&lt;=F12,"PASS","REVIEW")))</x:f>
+        <x:v>OPTIONAL</x:v>
       </x:c>
       <x:c r="H12" s="70" t="str">
         <x:v>ROA should equal net margin × asset turnover when average assets match.</x:v>
@@ -3077,8 +3188,8 @@
         <x:v>0.0001</x:v>
       </x:c>
       <x:c r="G13" s="48" t="str">
-        <x:f>IF(COUNT(C13:D13)&lt;2,"WAITING",IF(ABS(E13)&lt;=F13,"PASS","REVIEW"))</x:f>
-        <x:v>WAITING</x:v>
+        <x:f>IF('Student Calculations'!C13="","OPTIONAL",IF(COUNT(C13:D13)&lt;2,"WAITING",IF(ABS(E13)&lt;=F13,"PASS","REVIEW")))</x:f>
+        <x:v>OPTIONAL</x:v>
       </x:c>
       <x:c r="H13" s="70" t="str">
         <x:v>ROA should equal net margin × asset turnover when average assets match.</x:v>
@@ -3143,9 +3254,9 @@
         <x:v>Concise driver-based recommendation</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="34" customHeight="1">
+    <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="215" t="str">
-        <x:v>Write 4–6 sentences. Choose the stronger firm or benchmark position; cite one profitability or DuPont driver, one liquidity/leverage trade-off, the operating-expense test, and one monitoring trigger.</x:v>
+        <x:v>After class: write 4–6 sentences in A19. Compare the retailers using a profitability/DuPont driver, liquidity or leverage, interest coverage, the expense test, and a monitoring trigger.</x:v>
       </x:c>
       <x:c r="B18" s="216"/>
       <x:c r="C18" s="216"/>
@@ -3207,7 +3318,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="223" t="str">
-        <x:v>A PASS status confirms that the supplied statements tie and the student's average-denominator formulas reconcile. It does not mean every benchmark is universally appropriate; the recommendation must still explain context and trade-offs.</x:v>
+        <x:v>PASS checks core completion and internal consistency, not the quality of the recommendation. Optional ratios may remain blank; illustrative references are not universal targets.</x:v>
       </x:c>
       <x:c r="B25" s="224"/>
       <x:c r="C25" s="224"/>
@@ -3269,7 +3380,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>BUS311 · intro-m04-l01 · FactSet required · student starter</x:v>
+        <x:v>BUS311 · intro-m04-l01 · supplied-data practice</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
@@ -3290,7 +3401,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="70" t="str">
-        <x:v>Read the M04 pre-reading and confirm the denominator rule for each family.</x:v>
+        <x:v>In class: complete Class Practice alongside slides 7–12.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -3298,7 +3409,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="70" t="str">
-        <x:v>Verify source values, units, period, currency, and debt definition.</x:v>
+        <x:v>After class: compare the two fictional retailers using supplied Company Data.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -3306,7 +3417,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="70" t="str">
-        <x:v>Complete the two-firm ratio calculations with auditable Excel formulas.</x:v>
+        <x:v>Complete the eight CORE ratio rows for both firms; remaining rows are optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -3327,7 +3438,7 @@
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="10" t="str">
-        <x:v>FactSet / source documentation</x:v>
+        <x:v>Supplied case data / reference documentation</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3344,31 +3455,37 @@
         <x:v>Source note</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="40" customHeight="1">
       <x:c r="A14" s="91" t="str">
         <x:v>Company identifiers</x:v>
       </x:c>
-      <x:c r="B14" s="174"/>
+      <x:c r="B14" s="174" t="str">
+        <x:v>TechStyle Retail and Urban Goods: fictional classroom cases</x:v>
+      </x:c>
       <x:c r="C14" s="174"/>
       <x:c r="D14" s="232"/>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="40" customHeight="1">
       <x:c r="A15" s="91" t="str">
         <x:v>Balance-sheet values</x:v>
       </x:c>
-      <x:c r="B15" s="174"/>
+      <x:c r="B15" s="174" t="str">
+        <x:v>Company Data: supplied year-end balances</x:v>
+      </x:c>
       <x:c r="C15" s="174"/>
       <x:c r="D15" s="232"/>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="40" customHeight="1">
       <x:c r="A16" s="91" t="str">
         <x:v>Income-statement values</x:v>
       </x:c>
-      <x:c r="B16" s="174"/>
+      <x:c r="B16" s="174" t="str">
+        <x:v>Company Data: supplied annual income statements</x:v>
+      </x:c>
       <x:c r="C16" s="174"/>
       <x:c r="D16" s="232"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="40" customHeight="1">
       <x:c r="A17" s="91" t="str">
         <x:v>Debt definition</x:v>
       </x:c>
@@ -3378,11 +3495,13 @@
       <x:c r="C17" s="174"/>
       <x:c r="D17" s="232"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="40" customHeight="1">
       <x:c r="A18" s="101" t="str">
         <x:v>Comparison benchmark</x:v>
       </x:c>
-      <x:c r="B18" s="233"/>
+      <x:c r="B18" s="233" t="str">
+        <x:v>Illustrative classroom references; not observed industry averages</x:v>
+      </x:c>
       <x:c r="C18" s="233"/>
       <x:c r="D18" s="234"/>
     </x:row>
@@ -3435,7 +3554,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="223" t="str">
-        <x:v>Use FactSet definitions only when the field, company, fiscal period, units, currency, and retrieval date are documented. A correct-looking ratio built from mismatched periods or definitions is not valid analysis.</x:v>
+        <x:v>No FactSet retrieval is required for M04. A later real-company extension would require company, field, period, currency, units, and retrieval date. Lemonade is reserved for later use.</x:v>
       </x:c>
       <x:c r="B27" s="224"/>
       <x:c r="C27" s="224"/>
@@ -3462,4 +3581,419 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="243" t="str">
+        <x:v>M04 | Class Practice — same example as the slides</x:v>
+      </x:c>
+      <x:c r="B1" s="243"/>
+      <x:c r="C1" s="243"/>
+      <x:c r="D1" s="243"/>
+      <x:c r="E1" s="243"/>
+      <x:c r="F1" s="243"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="244" t="str">
+        <x:v>Slides 7–12: enter five formulas in E5:E9, then explain the DuPont drivers. Return here for the in-class brief.</x:v>
+      </x:c>
+      <x:c r="B2" s="241"/>
+      <x:c r="C2" s="241"/>
+      <x:c r="D2" s="241"/>
+      <x:c r="E2" s="241"/>
+      <x:c r="F2" s="241"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="241"/>
+      <x:c r="B3" s="241"/>
+      <x:c r="C3" s="241"/>
+      <x:c r="D3" s="241"/>
+      <x:c r="E3" s="241"/>
+      <x:c r="F3" s="241"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="255" t="str">
+        <x:v>Given inputs (USD)</x:v>
+      </x:c>
+      <x:c r="B4" s="255" t="str">
+        <x:v>Amount</x:v>
+      </x:c>
+      <x:c r="C4" s="241"/>
+      <x:c r="D4" s="255" t="str">
+        <x:v>Five core signals</x:v>
+      </x:c>
+      <x:c r="E4" s="255" t="str">
+        <x:v>Your formula</x:v>
+      </x:c>
+      <x:c r="F4" s="255" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="241" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="B5" s="247" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="C5" s="241"/>
+      <x:c r="D5" s="241" t="str">
+        <x:v>Current ratio</x:v>
+      </x:c>
+      <x:c r="E5" s="249"/>
+      <x:c r="F5" s="244" t="str">
+        <x:v>Current assets / current liabilities</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="241" t="str">
+        <x:v>Cost of goods sold</x:v>
+      </x:c>
+      <x:c r="B6" s="247" t="n">
+        <x:v>48000</x:v>
+      </x:c>
+      <x:c r="C6" s="241"/>
+      <x:c r="D6" s="241" t="str">
+        <x:v>Gross margin</x:v>
+      </x:c>
+      <x:c r="E6" s="250"/>
+      <x:c r="F6" s="244" t="str">
+        <x:v>(Revenue - COGS) / revenue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="241" t="str">
+        <x:v>Net income</x:v>
+      </x:c>
+      <x:c r="B7" s="247" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="C7" s="241"/>
+      <x:c r="D7" s="241" t="str">
+        <x:v>Asset turnover</x:v>
+      </x:c>
+      <x:c r="E7" s="249"/>
+      <x:c r="F7" s="244" t="str">
+        <x:v>Revenue / average assets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="241" t="str">
+        <x:v>Average assets</x:v>
+      </x:c>
+      <x:c r="B8" s="247" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C8" s="241"/>
+      <x:c r="D8" s="241" t="str">
+        <x:v>Debt ratio</x:v>
+      </x:c>
+      <x:c r="E8" s="250"/>
+      <x:c r="F8" s="244" t="str">
+        <x:v>Total debt / ending assets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="241" t="str">
+        <x:v>Current assets</x:v>
+      </x:c>
+      <x:c r="B9" s="247" t="n">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="C9" s="241"/>
+      <x:c r="D9" s="241" t="str">
+        <x:v>ROE</x:v>
+      </x:c>
+      <x:c r="E9" s="250"/>
+      <x:c r="F9" s="244" t="str">
+        <x:v>Net income / average equity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="241" t="str">
+        <x:v>Current liabilities</x:v>
+      </x:c>
+      <x:c r="B10" s="247" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="C10" s="241"/>
+      <x:c r="D10" s="241"/>
+      <x:c r="E10" s="241"/>
+      <x:c r="F10" s="244"/>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="241" t="str">
+        <x:v>Total debt</x:v>
+      </x:c>
+      <x:c r="B11" s="247" t="n">
+        <x:v>44000</x:v>
+      </x:c>
+      <x:c r="C11" s="241"/>
+      <x:c r="D11" s="241"/>
+      <x:c r="E11" s="241"/>
+      <x:c r="F11" s="244"/>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="241" t="str">
+        <x:v>Ending assets</x:v>
+      </x:c>
+      <x:c r="B12" s="247" t="n">
+        <x:v>88000</x:v>
+      </x:c>
+      <x:c r="C12" s="241"/>
+      <x:c r="D12" s="255" t="str">
+        <x:v>DuPont bridge</x:v>
+      </x:c>
+      <x:c r="E12" s="255" t="str">
+        <x:v>Linked result</x:v>
+      </x:c>
+      <x:c r="F12" s="256" t="str">
+        <x:v>Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="241" t="str">
+        <x:v>Beginning equity</x:v>
+      </x:c>
+      <x:c r="B13" s="247" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="C13" s="241"/>
+      <x:c r="D13" s="241" t="str">
+        <x:v>Net margin</x:v>
+      </x:c>
+      <x:c r="E13" s="251" t="n">
+        <x:f>B7/B5</x:f>
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F13" s="244" t="str">
+        <x:v>After all expenses; compare with gross margin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="241" t="str">
+        <x:v>Ending equity</x:v>
+      </x:c>
+      <x:c r="B14" s="247" t="n">
+        <x:v>32000</x:v>
+      </x:c>
+      <x:c r="C14" s="241"/>
+      <x:c r="D14" s="241" t="str">
+        <x:v>Asset turnover</x:v>
+      </x:c>
+      <x:c r="E14" s="252" t="str">
+        <x:f>IF(E7="","",E7)</x:f>
+      </x:c>
+      <x:c r="F14" s="244" t="str">
+        <x:v>Same ratio as E7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="241"/>
+      <x:c r="B15" s="241"/>
+      <x:c r="C15" s="241"/>
+      <x:c r="D15" s="241" t="str">
+        <x:v>Equity multiplier</x:v>
+      </x:c>
+      <x:c r="E15" s="252" t="n">
+        <x:f>B8/AVERAGE(B13:B14)</x:f>
+        <x:v>2.6666666666666665</x:v>
+      </x:c>
+      <x:c r="F15" s="244" t="str">
+        <x:v>Use the full value; display rounds to 2.67x</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="241"/>
+      <x:c r="B16" s="241"/>
+      <x:c r="C16" s="241"/>
+      <x:c r="D16" s="241" t="str">
+        <x:v>DuPont ROE</x:v>
+      </x:c>
+      <x:c r="E16" s="251" t="str">
+        <x:f>IF(E14="","",E13*E14*E15)</x:f>
+      </x:c>
+      <x:c r="F16" s="244" t="str">
+        <x:v>Net margin x turnover x equity multiplier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="241"/>
+      <x:c r="B17" s="241"/>
+      <x:c r="C17" s="241"/>
+      <x:c r="D17" s="241" t="str">
+        <x:v>Reconciliation difference</x:v>
+      </x:c>
+      <x:c r="E17" s="251" t="str">
+        <x:f>IF(OR(E9="",E16=""),"",E16-E9)</x:f>
+      </x:c>
+      <x:c r="F17" s="244" t="str">
+        <x:v>Should be zero when ROE is consistent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="241"/>
+      <x:c r="B18" s="241"/>
+      <x:c r="C18" s="241"/>
+      <x:c r="D18" s="241"/>
+      <x:c r="E18" s="241"/>
+      <x:c r="F18" s="241"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="241"/>
+      <x:c r="B19" s="241"/>
+      <x:c r="C19" s="241"/>
+      <x:c r="D19" s="241"/>
+      <x:c r="E19" s="241"/>
+      <x:c r="F19" s="241"/>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="241" t="str">
+        <x:v>In-class brief: two sentences using two ratios, a driver, a risk, and a follow-up data request.</x:v>
+      </x:c>
+      <x:c r="B20" s="241"/>
+      <x:c r="C20" s="241"/>
+      <x:c r="D20" s="241"/>
+      <x:c r="E20" s="241"/>
+      <x:c r="F20" s="241"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="254"/>
+      <x:c r="B21" s="254"/>
+      <x:c r="C21" s="254"/>
+      <x:c r="D21" s="254"/>
+      <x:c r="E21" s="254"/>
+      <x:c r="F21" s="254"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="254"/>
+      <x:c r="B22" s="254"/>
+      <x:c r="C22" s="254"/>
+      <x:c r="D22" s="254"/>
+      <x:c r="E22" s="254"/>
+      <x:c r="F22" s="254"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="254"/>
+      <x:c r="B23" s="254"/>
+      <x:c r="C23" s="254"/>
+      <x:c r="D23" s="254"/>
+      <x:c r="E23" s="254"/>
+      <x:c r="F23" s="254"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="254"/>
+      <x:c r="B24" s="254"/>
+      <x:c r="C24" s="254"/>
+      <x:c r="D24" s="254"/>
+      <x:c r="E24" s="254"/>
+      <x:c r="F24" s="254"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="241"/>
+      <x:c r="B25" s="241"/>
+      <x:c r="C25" s="241"/>
+      <x:c r="D25" s="241"/>
+      <x:c r="E25" s="241"/>
+      <x:c r="F25" s="241"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="241"/>
+      <x:c r="B26" s="241"/>
+      <x:c r="C26" s="241"/>
+      <x:c r="D26" s="241"/>
+      <x:c r="E26" s="241"/>
+      <x:c r="F26" s="241"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="244" t="str">
+        <x:v>After class: move to Company Data and Student Calculations. The two-retailer case uses different data deliberately. Complete CORE rows 6, 10, 12, 14, 17, 18, 22, and 23; optional rows may stay blank.</x:v>
+      </x:c>
+      <x:c r="B27" s="241"/>
+      <x:c r="C27" s="241"/>
+      <x:c r="D27" s="241"/>
+      <x:c r="E27" s="241"/>
+      <x:c r="F27" s="241"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="241"/>
+      <x:c r="B28" s="241"/>
+      <x:c r="C28" s="241"/>
+      <x:c r="D28" s="241"/>
+      <x:c r="E28" s="241"/>
+      <x:c r="F28" s="241"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="241"/>
+      <x:c r="B29" s="241"/>
+      <x:c r="C29" s="241"/>
+      <x:c r="D29" s="241"/>
+      <x:c r="E29" s="241"/>
+      <x:c r="F29" s="241"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="244" t="str">
+        <x:v>Source: instructor-created classroom example matching the M04 slides. No external retrieval required.</x:v>
+      </x:c>
+      <x:c r="B30" s="241"/>
+      <x:c r="C30" s="241"/>
+      <x:c r="D30" s="241"/>
+      <x:c r="E30" s="241"/>
+      <x:c r="F30" s="241"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="241"/>
+      <x:c r="B31" s="241"/>
+      <x:c r="C31" s="241"/>
+      <x:c r="D31" s="241"/>
+      <x:c r="E31" s="241"/>
+      <x:c r="F31" s="241"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="241"/>
+      <x:c r="B32" s="241"/>
+      <x:c r="C32" s="241"/>
+      <x:c r="D32" s="241"/>
+      <x:c r="E32" s="241"/>
+      <x:c r="F32" s="241"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="241"/>
+      <x:c r="B33" s="241"/>
+      <x:c r="C33" s="241"/>
+      <x:c r="D33" s="241"/>
+      <x:c r="E33" s="241"/>
+      <x:c r="F33" s="241"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="241"/>
+      <x:c r="B34" s="241"/>
+      <x:c r="C34" s="241"/>
+      <x:c r="D34" s="241"/>
+      <x:c r="E34" s="241"/>
+      <x:c r="F34" s="241"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A20:F20"/>
+    <x:mergeCell ref="A21:F24"/>
+    <x:mergeCell ref="A27:F28"/>
+    <x:mergeCell ref="A30:F31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
+++ b/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
@@ -3,13 +3,13 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R21b5ceddb101428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Practice" sheetId="8" r:id="Rfed5955485f74439"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Data" sheetId="2" r:id="Rfaa76ee0da3545dc"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Calculations" sheetId="3" r:id="R5c75078c7551405b"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuPont &amp; Driver" sheetId="4" r:id="R8fee8ed6ebd84027"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Dashboard" sheetId="5" r:id="R01b9735ffe2d4dc6"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Recommendation" sheetId="6" r:id="Ra86f998e0ae84e67"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="7" r:id="Rde0ee913d44d41f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Practice" sheetId="8" r:id="Rfed5955485f74439"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
+++ b/01-INTRO/M04/bus311-intro-m04-l01-starter.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R21b5ceddb101428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Practice" sheetId="8" r:id="Rfed5955485f74439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Data" sheetId="2" r:id="Rfaa76ee0da3545dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Calculations" sheetId="3" r:id="R5c75078c7551405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuPont &amp; Driver" sheetId="4" r:id="R8fee8ed6ebd84027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Dashboard" sheetId="5" r:id="R01b9735ffe2d4dc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Recommendation" sheetId="6" r:id="Ra86f998e0ae84e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="7" r:id="Rde0ee913d44d41f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R09b55400c8064acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Practice" sheetId="8" r:id="R2be991744ca94d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Data" sheetId="2" r:id="Ra83556b481f64478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Calculations" sheetId="3" r:id="Rca20150d615f425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DuPont &amp; Driver" sheetId="4" r:id="R07abe502b7f6489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Dashboard" sheetId="5" r:id="R4ebf5dfbdda54d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Recommendation" sheetId="6" r:id="Rd6ed272f52d34921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="7" r:id="Rbe27d6de17f94a13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +29,7 @@
     <x:numFmt numFmtId="205" formatCode="$#,##0"/>
     <x:numFmt numFmtId="206" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -110,8 +110,14 @@
       <x:sz val="11"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -186,6 +192,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDCE8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF192640"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -312,7 +323,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="257">
+  <x:cellXfs count="263">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -866,11 +877,23 @@
     <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="6">
+  <x:dxfs count="66">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -934,6 +957,606 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD6F2DD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF854D0E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0C2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1151,19 +1774,19 @@
         <x:v>BUS311 | Ratio Analysis and Corporate Performance</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="46" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>M04: Class Practice follows the slides. After class, compare two retailers using eight core ratios, DuPont, and one operating test.</x:v>
+        <x:v>Use financial ratios, DuPont, and an expense-reduction test to explain business performance and support a recommendation. Complete calculations in class; finish explanations after class before submitting to Canvas.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
-      <x:c r="A4" s="10" t="str">
-        <x:v>Purpose and deliverable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A4" s="235" t="str">
+        <x:v>Purpose and deliverables</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="94" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>In class: five ratios and a short brief on Class Practice. After class: eight core ratios per firm (16 formulas), an expense test, and a 4–6 sentence recommendation. Optional ratios are reference only.</x:v>
+        <x:v>In class: complete Class Practice E5:E9, all eight CORE ratio rows for both retailers, and the DuPont &amp; Driver expense test. After class: finish the Class Practice brief (A21), driver explanation (B29), and retailer recommendation (A19 on Checks &amp; Recommendation). Submit one completed Excel workbook to Canvas.</x:v>
       </x:c>
       <x:c r="B5" s="15"/>
       <x:c r="C5" s="15"/>
@@ -1199,70 +1822,70 @@
         <x:v>Visible checkpoint</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="44" customHeight="1">
+    <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>Start with Class Practice during slides 7–12.</x:v>
+        <x:v>In class: open Class Practice (second tab).</x:v>
       </x:c>
       <x:c r="C10" s="32" t="str">
-        <x:v>Use the same $120,000-revenue example as the deck.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="44" customHeight="1">
+        <x:v>Calculate five ratios in E5:E9 and review the linked DuPont bridge.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>After class, use Company Data and Student Calculations.</x:v>
+        <x:v>In class: use Company Data and Student Calculations.</x:v>
       </x:c>
       <x:c r="C11" s="32" t="str">
-        <x:v>Complete the eight CORE rows for both retailers.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+        <x:v>Complete CORE rows 6, 10, 12, 14, 17, 18, 22, 23 for both firms; check feedback in F:G.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>Read DuPont &amp; Driver after entering the core formulas.</x:v>
+        <x:v>In class: open DuPont &amp; Driver.</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>Reconcile ROE and explain the three drivers.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="44" customHeight="1">
+        <x:v>Reconcile direct and DuPont ROE; the differences in row 16 should equal zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>Enter an expense-reduction assumption in DuPont &amp; Driver!B20.</x:v>
+        <x:v>In class: predict, then enter 1% in DuPont &amp; Driver!B20.</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Interpret the effect in B29; use a plausible percentage.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="44" customHeight="1">
+        <x:v>Compare the linked scenario results. Finish the explanation in B29 after class.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>Read the linked Ratio Dashboard.</x:v>
+        <x:v>In class: review Ratio Dashboard.</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Compare drivers, coverage, and illustrative references.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="44" customHeight="1">
+        <x:v>Compare profitability, asset use, financing, coverage, and the expense test.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="34" t="str">
-        <x:v>Review Checks &amp; Recommendation and write your response.</x:v>
+        <x:v>After class: finish explanations, review, and submit.</x:v>
       </x:c>
       <x:c r="C15" s="35" t="str">
-        <x:v>Complete core work and explain one monitoring trigger.</x:v>
+        <x:v>Complete Class Practice A21, DuPont &amp; Driver B29, and Checks &amp; Recommendation A19. Submit the workbook to Canvas.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
@@ -1352,9 +1975,9 @@
         <x:v>Lemonade Stand is deferred; it is not part of the M04 submission.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="46" customHeight="1">
+    <x:row r="30" ht="70" customHeight="1">
       <x:c r="A30" s="60" t="str">
-        <x:v>Use supplied fictional case data; no FactSet retrieval is required. Complete core comparison work after class. Optional ratios provide definitions for later practice.</x:v>
+        <x:v>Before Canvas submission: confirm calculations are complete, review any Check or REVIEW messages, and finish all three written responses. Correct and PASS check numbers or completion, not the quality of your reasoning. Optional ratios may remain blank.</x:v>
       </x:c>
       <x:c r="B30" s="61"/>
       <x:c r="C30" s="61"/>
@@ -1398,6 +2021,421 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="243" t="str">
+        <x:v>M04 | Class Practice — same example as the slides</x:v>
+      </x:c>
+      <x:c r="B1" s="243"/>
+      <x:c r="C1" s="243"/>
+      <x:c r="D1" s="243"/>
+      <x:c r="E1" s="243"/>
+      <x:c r="F1" s="243"/>
+    </x:row>
+    <x:row r="2" ht="48" customHeight="1">
+      <x:c r="A2" s="244" t="str">
+        <x:v>In class: enter five formulas in E5:E9 and review the linked DuPont drivers. Draft the brief in A21; you may finish the explanation after class before Canvas submission.</x:v>
+      </x:c>
+      <x:c r="B2" s="241"/>
+      <x:c r="C2" s="241"/>
+      <x:c r="D2" s="241"/>
+      <x:c r="E2" s="241"/>
+      <x:c r="F2" s="241"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="241"/>
+      <x:c r="B3" s="241"/>
+      <x:c r="C3" s="241"/>
+      <x:c r="D3" s="241"/>
+      <x:c r="E3" s="241"/>
+      <x:c r="F3" s="241"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="255" t="str">
+        <x:v>Given inputs (USD)</x:v>
+      </x:c>
+      <x:c r="B4" s="255" t="str">
+        <x:v>Amount</x:v>
+      </x:c>
+      <x:c r="C4" s="241"/>
+      <x:c r="D4" s="255" t="str">
+        <x:v>Five core signals</x:v>
+      </x:c>
+      <x:c r="E4" s="255" t="str">
+        <x:v>Your formula</x:v>
+      </x:c>
+      <x:c r="F4" s="255" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="241" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="B5" s="247" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="C5" s="241"/>
+      <x:c r="D5" s="241" t="str">
+        <x:v>Current ratio</x:v>
+      </x:c>
+      <x:c r="E5" s="249"/>
+      <x:c r="F5" s="244" t="str">
+        <x:v>Current assets / current liabilities</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="241" t="str">
+        <x:v>Cost of goods sold</x:v>
+      </x:c>
+      <x:c r="B6" s="247" t="n">
+        <x:v>48000</x:v>
+      </x:c>
+      <x:c r="C6" s="241"/>
+      <x:c r="D6" s="241" t="str">
+        <x:v>Gross margin</x:v>
+      </x:c>
+      <x:c r="E6" s="250"/>
+      <x:c r="F6" s="244" t="str">
+        <x:v>(Revenue - COGS) / revenue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="241" t="str">
+        <x:v>Net income</x:v>
+      </x:c>
+      <x:c r="B7" s="247" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="C7" s="241"/>
+      <x:c r="D7" s="241" t="str">
+        <x:v>Asset turnover</x:v>
+      </x:c>
+      <x:c r="E7" s="249"/>
+      <x:c r="F7" s="244" t="str">
+        <x:v>Revenue / average assets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="241" t="str">
+        <x:v>Average assets</x:v>
+      </x:c>
+      <x:c r="B8" s="247" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C8" s="241"/>
+      <x:c r="D8" s="241" t="str">
+        <x:v>Debt ratio</x:v>
+      </x:c>
+      <x:c r="E8" s="250"/>
+      <x:c r="F8" s="244" t="str">
+        <x:v>Total debt / ending assets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="241" t="str">
+        <x:v>Current assets</x:v>
+      </x:c>
+      <x:c r="B9" s="247" t="n">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="C9" s="241"/>
+      <x:c r="D9" s="241" t="str">
+        <x:v>ROE</x:v>
+      </x:c>
+      <x:c r="E9" s="250"/>
+      <x:c r="F9" s="244" t="str">
+        <x:v>Net income / average equity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="241" t="str">
+        <x:v>Current liabilities</x:v>
+      </x:c>
+      <x:c r="B10" s="247" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="C10" s="241"/>
+      <x:c r="D10" s="241"/>
+      <x:c r="E10" s="241"/>
+      <x:c r="F10" s="244"/>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="241" t="str">
+        <x:v>Total debt</x:v>
+      </x:c>
+      <x:c r="B11" s="247" t="n">
+        <x:v>44000</x:v>
+      </x:c>
+      <x:c r="C11" s="241"/>
+      <x:c r="D11" s="241"/>
+      <x:c r="E11" s="241"/>
+      <x:c r="F11" s="244"/>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="241" t="str">
+        <x:v>Ending assets</x:v>
+      </x:c>
+      <x:c r="B12" s="247" t="n">
+        <x:v>88000</x:v>
+      </x:c>
+      <x:c r="C12" s="241"/>
+      <x:c r="D12" s="255" t="str">
+        <x:v>DuPont bridge</x:v>
+      </x:c>
+      <x:c r="E12" s="255" t="str">
+        <x:v>Linked result</x:v>
+      </x:c>
+      <x:c r="F12" s="256" t="str">
+        <x:v>Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="241" t="str">
+        <x:v>Beginning equity</x:v>
+      </x:c>
+      <x:c r="B13" s="247" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="C13" s="241"/>
+      <x:c r="D13" s="241" t="str">
+        <x:v>Net margin</x:v>
+      </x:c>
+      <x:c r="E13" s="251" t="n">
+        <x:f>B7/B5</x:f>
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F13" s="244" t="str">
+        <x:v>After all expenses; compare with gross margin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="241" t="str">
+        <x:v>Ending equity</x:v>
+      </x:c>
+      <x:c r="B14" s="247" t="n">
+        <x:v>32000</x:v>
+      </x:c>
+      <x:c r="C14" s="241"/>
+      <x:c r="D14" s="241" t="str">
+        <x:v>Asset turnover</x:v>
+      </x:c>
+      <x:c r="E14" s="252" t="str">
+        <x:f>IF(E7="","",E7)</x:f>
+      </x:c>
+      <x:c r="F14" s="244" t="str">
+        <x:v>Same ratio as E7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="241"/>
+      <x:c r="B15" s="241"/>
+      <x:c r="C15" s="241"/>
+      <x:c r="D15" s="241" t="str">
+        <x:v>Equity multiplier</x:v>
+      </x:c>
+      <x:c r="E15" s="252" t="n">
+        <x:f>B8/AVERAGE(B13:B14)</x:f>
+        <x:v>2.6666666666666665</x:v>
+      </x:c>
+      <x:c r="F15" s="244" t="str">
+        <x:v>Use the full value; display rounds to 2.67x</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="241"/>
+      <x:c r="B16" s="241"/>
+      <x:c r="C16" s="241"/>
+      <x:c r="D16" s="241" t="str">
+        <x:v>DuPont ROE</x:v>
+      </x:c>
+      <x:c r="E16" s="251" t="str">
+        <x:f>IF(E14="","",E13*E14*E15)</x:f>
+      </x:c>
+      <x:c r="F16" s="244" t="str">
+        <x:v>Net margin x turnover x equity multiplier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="241"/>
+      <x:c r="B17" s="241"/>
+      <x:c r="C17" s="241"/>
+      <x:c r="D17" s="241" t="str">
+        <x:v>Reconciliation difference</x:v>
+      </x:c>
+      <x:c r="E17" s="251" t="str">
+        <x:f>IF(OR(E9="",E16=""),"",E16-E9)</x:f>
+      </x:c>
+      <x:c r="F17" s="244" t="str">
+        <x:v>Should be zero when ROE is consistent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="241"/>
+      <x:c r="B18" s="241"/>
+      <x:c r="C18" s="241"/>
+      <x:c r="D18" s="241"/>
+      <x:c r="E18" s="241"/>
+      <x:c r="F18" s="241"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="241"/>
+      <x:c r="B19" s="241"/>
+      <x:c r="C19" s="241"/>
+      <x:c r="D19" s="241"/>
+      <x:c r="E19" s="241"/>
+      <x:c r="F19" s="241"/>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="244" t="str">
+        <x:v>Written deliverable in A21: two sentences using two ratios, a driver, a risk, and a follow-up data request.</x:v>
+      </x:c>
+      <x:c r="B20" s="241"/>
+      <x:c r="C20" s="241"/>
+      <x:c r="D20" s="241"/>
+      <x:c r="E20" s="241"/>
+      <x:c r="F20" s="241"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="254"/>
+      <x:c r="B21" s="254"/>
+      <x:c r="C21" s="254"/>
+      <x:c r="D21" s="254"/>
+      <x:c r="E21" s="254"/>
+      <x:c r="F21" s="254"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="254"/>
+      <x:c r="B22" s="254"/>
+      <x:c r="C22" s="254"/>
+      <x:c r="D22" s="254"/>
+      <x:c r="E22" s="254"/>
+      <x:c r="F22" s="254"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="254"/>
+      <x:c r="B23" s="254"/>
+      <x:c r="C23" s="254"/>
+      <x:c r="D23" s="254"/>
+      <x:c r="E23" s="254"/>
+      <x:c r="F23" s="254"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="254"/>
+      <x:c r="B24" s="254"/>
+      <x:c r="C24" s="254"/>
+      <x:c r="D24" s="254"/>
+      <x:c r="E24" s="254"/>
+      <x:c r="F24" s="254"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="241"/>
+      <x:c r="B25" s="241"/>
+      <x:c r="C25" s="241"/>
+      <x:c r="D25" s="241"/>
+      <x:c r="E25" s="241"/>
+      <x:c r="F25" s="241"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="241"/>
+      <x:c r="B26" s="241"/>
+      <x:c r="C26" s="241"/>
+      <x:c r="D26" s="241"/>
+      <x:c r="E26" s="241"/>
+      <x:c r="F26" s="241"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="244" t="str">
+        <x:v>In class: continue to Company Data and Student Calculations for the two-retailer case. Complete CORE rows 6, 10, 12, 14, 17, 18, 22, and 23 for both firms. Optional rows may remain blank.</x:v>
+      </x:c>
+      <x:c r="B27" s="241"/>
+      <x:c r="C27" s="241"/>
+      <x:c r="D27" s="241"/>
+      <x:c r="E27" s="241"/>
+      <x:c r="F27" s="241"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="241"/>
+      <x:c r="B28" s="241"/>
+      <x:c r="C28" s="241"/>
+      <x:c r="D28" s="241"/>
+      <x:c r="E28" s="241"/>
+      <x:c r="F28" s="241"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="241"/>
+      <x:c r="B29" s="241"/>
+      <x:c r="C29" s="241"/>
+      <x:c r="D29" s="241"/>
+      <x:c r="E29" s="241"/>
+      <x:c r="F29" s="241"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="244" t="str">
+        <x:v>Source: instructor-created classroom example matching the M04 slides. No external retrieval required.</x:v>
+      </x:c>
+      <x:c r="B30" s="241"/>
+      <x:c r="C30" s="241"/>
+      <x:c r="D30" s="241"/>
+      <x:c r="E30" s="241"/>
+      <x:c r="F30" s="241"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="241"/>
+      <x:c r="B31" s="241"/>
+      <x:c r="C31" s="241"/>
+      <x:c r="D31" s="241"/>
+      <x:c r="E31" s="241"/>
+      <x:c r="F31" s="241"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="241"/>
+      <x:c r="B32" s="241"/>
+      <x:c r="C32" s="241"/>
+      <x:c r="D32" s="241"/>
+      <x:c r="E32" s="241"/>
+      <x:c r="F32" s="241"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="241"/>
+      <x:c r="B33" s="241"/>
+      <x:c r="C33" s="241"/>
+      <x:c r="D33" s="241"/>
+      <x:c r="E33" s="241"/>
+      <x:c r="F33" s="241"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="241"/>
+      <x:c r="B34" s="241"/>
+      <x:c r="C34" s="241"/>
+      <x:c r="D34" s="241"/>
+      <x:c r="E34" s="241"/>
+      <x:c r="F34" s="241"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A20:F20"/>
+    <x:mergeCell ref="A21:F24"/>
+    <x:mergeCell ref="A27:F28"/>
+    <x:mergeCell ref="A30:F31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
@@ -1838,7 +2876,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1847,6 +2885,8 @@
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1854,9 +2894,9 @@
         <x:v>Student Calculations | Ratio Families</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="48" customHeight="1">
+    <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>After class: enter formulas in yellow CORE rows for both firms. Optional rows may remain blank. All references are illustrative classroom assumptions, not industry targets.</x:v>
+        <x:v>Complete all eight CORE ratio rows for both firms in class. Feedback checks numeric results at displayed precision: Correct or Check. Optional rows may remain blank. Finish written explanations after class before Canvas submission.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -1874,6 +2914,12 @@
       </x:c>
       <x:c r="E4" s="151" t="str">
         <x:v>Definition / denominator contract</x:v>
+      </x:c>
+      <x:c r="F4" s="259" t="str">
+        <x:v>TechStyle check</x:v>
+      </x:c>
+      <x:c r="G4" s="259" t="str">
+        <x:v>Urban check</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
@@ -1897,6 +2943,12 @@
       <x:c r="E6" s="113" t="str">
         <x:v>Current Assets / Current Liabilities</x:v>
       </x:c>
+      <x:c r="F6" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B6)&gt;0,"",IF(NOT(ISNUMBER(B6)),"Check",IF(ROUND(B6,2)=ROUND('Company Data'!B15/'Company Data'!B20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G6" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C6)&gt;0,"",IF(NOT(ISNUMBER(C6)),"Check",IF(ROUND(C6,2)=ROUND('Company Data'!C15/'Company Data'!C20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="118" t="str">
@@ -1910,6 +2962,12 @@
       <x:c r="E7" s="113" t="str">
         <x:v>(Current Assets - Inventory) / Current Liabilities</x:v>
       </x:c>
+      <x:c r="F7" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B7)&gt;0,"",IF(NOT(ISNUMBER(B7)),"Check",IF(ROUND(B7,2)=ROUND(('Company Data'!B15-'Company Data'!B14)/'Company Data'!B20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G7" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C7)&gt;0,"",IF(NOT(ISNUMBER(C7)),"Check",IF(ROUND(C7,2)=ROUND(('Company Data'!C15-'Company Data'!C14)/'Company Data'!C20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="118" t="str">
@@ -1923,6 +2981,12 @@
       <x:c r="E8" s="113" t="str">
         <x:v>Cash / Current Liabilities</x:v>
       </x:c>
+      <x:c r="F8" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B8)&gt;0,"",IF(NOT(ISNUMBER(B8)),"Check",IF(ROUND(B8,2)=ROUND('Company Data'!B12/'Company Data'!B20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G8" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C8)&gt;0,"",IF(NOT(ISNUMBER(C8)),"Check",IF(ROUND(C8,2)=ROUND('Company Data'!C12/'Company Data'!C20,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="89" t="str">
@@ -1945,6 +3009,12 @@
       <x:c r="E10" s="113" t="str">
         <x:v>Gross Profit / Revenue</x:v>
       </x:c>
+      <x:c r="F10" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B10)&gt;0,"",IF(NOT(ISNUMBER(B10)),"Check",IF(ROUND(B10,3)=ROUND('Company Data'!B35/'Company Data'!B33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G10" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C10)&gt;0,"",IF(NOT(ISNUMBER(C10)),"Check",IF(ROUND(C10,3)=ROUND('Company Data'!C35/'Company Data'!C33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="118" t="str">
@@ -1958,6 +3028,12 @@
       <x:c r="E11" s="113" t="str">
         <x:v>EBIT / Revenue</x:v>
       </x:c>
+      <x:c r="F11" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B11)&gt;0,"",IF(NOT(ISNUMBER(B11)),"Check",IF(ROUND(B11,3)=ROUND('Company Data'!B37/'Company Data'!B33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G11" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C11)&gt;0,"",IF(NOT(ISNUMBER(C11)),"Check",IF(ROUND(C11,3)=ROUND('Company Data'!C37/'Company Data'!C33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="118" t="str">
@@ -1971,6 +3047,12 @@
       <x:c r="E12" s="113" t="str">
         <x:v>Net Income / Revenue</x:v>
       </x:c>
+      <x:c r="F12" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B12)&gt;0,"",IF(NOT(ISNUMBER(B12)),"Check",IF(ROUND(B12,3)=ROUND('Company Data'!B41/'Company Data'!B33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G12" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C12)&gt;0,"",IF(NOT(ISNUMBER(C12)),"Check",IF(ROUND(C12,3)=ROUND('Company Data'!C41/'Company Data'!C33,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="118" t="str">
@@ -1984,6 +3066,12 @@
       <x:c r="E13" s="113" t="str">
         <x:v>Net Income / Average Total Assets</x:v>
       </x:c>
+      <x:c r="F13" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B13)&gt;0,"",IF(NOT(ISNUMBER(B13)),"Check",IF(ROUND(B13,3)=ROUND('Company Data'!B41/AVERAGE('Company Data'!B17,'Company Data'!B29),3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G13" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C13)&gt;0,"",IF(NOT(ISNUMBER(C13)),"Check",IF(ROUND(C13,3)=ROUND('Company Data'!C41/AVERAGE('Company Data'!C17,'Company Data'!C29),3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="118" t="str">
@@ -1997,6 +3085,12 @@
       <x:c r="E14" s="113" t="str">
         <x:v>Net Income / Average Total Equity</x:v>
       </x:c>
+      <x:c r="F14" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B14)&gt;0,"",IF(NOT(ISNUMBER(B14)),"Check",IF(ROUND(B14,3)=ROUND('Company Data'!B41/AVERAGE('Company Data'!B24,'Company Data'!B30),3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G14" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C14)&gt;0,"",IF(NOT(ISNUMBER(C14)),"Check",IF(ROUND(C14,3)=ROUND('Company Data'!C41/AVERAGE('Company Data'!C24,'Company Data'!C30),3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="89" t="str">
@@ -2019,6 +3113,12 @@
       <x:c r="E16" s="113" t="str">
         <x:v>Total Debt (ST + LT) / Current Total Equity</x:v>
       </x:c>
+      <x:c r="F16" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B16)&gt;0,"",IF(NOT(ISNUMBER(B16)),"Check",IF(ROUND(B16,2)=ROUND('Company Data'!B22/'Company Data'!B24,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G16" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C16)&gt;0,"",IF(NOT(ISNUMBER(C16)),"Check",IF(ROUND(C16,2)=ROUND('Company Data'!C22/'Company Data'!C24,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="118" t="str">
@@ -2032,6 +3132,12 @@
       <x:c r="E17" s="113" t="str">
         <x:v>Total Debt (ST + LT) / Current Total Assets</x:v>
       </x:c>
+      <x:c r="F17" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B17)&gt;0,"",IF(NOT(ISNUMBER(B17)),"Check",IF(ROUND(B17,3)=ROUND('Company Data'!B22/'Company Data'!B17,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G17" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C17)&gt;0,"",IF(NOT(ISNUMBER(C17)),"Check",IF(ROUND(C17,3)=ROUND('Company Data'!C22/'Company Data'!C17,3),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="118" t="str">
@@ -2045,6 +3151,12 @@
       <x:c r="E18" s="113" t="str">
         <x:v>Average Total Assets / Average Total Equity</x:v>
       </x:c>
+      <x:c r="F18" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B18)&gt;0,"",IF(NOT(ISNUMBER(B18)),"Check",IF(ROUND(B18,2)=ROUND(AVERAGE('Company Data'!B17,'Company Data'!B29)/AVERAGE('Company Data'!B24,'Company Data'!B30),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G18" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C18)&gt;0,"",IF(NOT(ISNUMBER(C18)),"Check",IF(ROUND(C18,2)=ROUND(AVERAGE('Company Data'!C17,'Company Data'!C29)/AVERAGE('Company Data'!C24,'Company Data'!C30),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="89" t="str">
@@ -2067,6 +3179,12 @@
       <x:c r="E20" s="113" t="str">
         <x:v>COGS / Average Inventory</x:v>
       </x:c>
+      <x:c r="F20" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B20)&gt;0,"",IF(NOT(ISNUMBER(B20)),"Check",IF(ROUND(B20,2)=ROUND('Company Data'!B34/AVERAGE('Company Data'!B14,'Company Data'!B27),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G20" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C20)&gt;0,"",IF(NOT(ISNUMBER(C20)),"Check",IF(ROUND(C20,2)=ROUND('Company Data'!C34/AVERAGE('Company Data'!C14,'Company Data'!C27),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="118" t="str">
@@ -2080,6 +3198,12 @@
       <x:c r="E21" s="113" t="str">
         <x:v>Revenue / Average Accounts Receivable</x:v>
       </x:c>
+      <x:c r="F21" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B21)&gt;0,"",IF(NOT(ISNUMBER(B21)),"Check",IF(ROUND(B21,2)=ROUND('Company Data'!B33/AVERAGE('Company Data'!B13,'Company Data'!B28),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G21" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C21)&gt;0,"",IF(NOT(ISNUMBER(C21)),"Check",IF(ROUND(C21,2)=ROUND('Company Data'!C33/AVERAGE('Company Data'!C13,'Company Data'!C28),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="132" t="str">
@@ -2093,6 +3217,12 @@
       <x:c r="E22" s="116" t="str">
         <x:v>Revenue / Average Total Assets</x:v>
       </x:c>
+      <x:c r="F22" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B22)&gt;0,"",IF(NOT(ISNUMBER(B22)),"Check",IF(ROUND(B22,2)=ROUND('Company Data'!B33/AVERAGE('Company Data'!B17,'Company Data'!B29),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G22" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C22)&gt;0,"",IF(NOT(ISNUMBER(C22)),"Check",IF(ROUND(C22,2)=ROUND('Company Data'!C33/AVERAGE('Company Data'!C17,'Company Data'!C29),2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="107" t="str">
@@ -2105,6 +3235,12 @@
       </x:c>
       <x:c r="E23" s="107" t="str">
         <x:v>EBIT / Interest Expense (same annual period)</x:v>
+      </x:c>
+      <x:c r="F23" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(B23)&gt;0,"",IF(NOT(ISNUMBER(B23)),"Check",IF(ROUND(B23,2)=ROUND('Company Data'!B37/'Company Data'!B38,2),"Correct","Check"))),"Check")</x:f>
+      </x:c>
+      <x:c r="G23" s="262" t="str">
+        <x:f>IFERROR(IF(COUNTBLANK(C23)&gt;0,"",IF(NOT(ISNUMBER(C23)),"Check",IF(ROUND(C23,2)=ROUND('Company Data'!C37/'Company Data'!C38,2),"Correct","Check"))),"Check")</x:f>
       </x:c>
     </x:row>
     <x:row r="24" ht="46" customHeight="1">
@@ -2126,11 +3262,251 @@
     <x:mergeCell ref="A19:E19"/>
     <x:mergeCell ref="A24:E24"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="F6:F6">
+    <x:cfRule type="expression" dxfId="6" priority="1">
+      <x:formula>F6="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="2">
+      <x:formula>F6="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F7:F7">
+    <x:cfRule type="expression" dxfId="8" priority="3">
+      <x:formula>F7="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="9" priority="4">
+      <x:formula>F7="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F8:F8">
+    <x:cfRule type="expression" dxfId="10" priority="5">
+      <x:formula>F8="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="11" priority="6">
+      <x:formula>F8="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F10:F10">
+    <x:cfRule type="expression" dxfId="12" priority="7">
+      <x:formula>F10="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="13" priority="8">
+      <x:formula>F10="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F11:F11">
+    <x:cfRule type="expression" dxfId="14" priority="9">
+      <x:formula>F11="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="15" priority="10">
+      <x:formula>F11="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F12:F12">
+    <x:cfRule type="expression" dxfId="16" priority="11">
+      <x:formula>F12="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="17" priority="12">
+      <x:formula>F12="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F13:F13">
+    <x:cfRule type="expression" dxfId="18" priority="13">
+      <x:formula>F13="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="19" priority="14">
+      <x:formula>F13="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F14:F14">
+    <x:cfRule type="expression" dxfId="20" priority="15">
+      <x:formula>F14="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="21" priority="16">
+      <x:formula>F14="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F16:F16">
+    <x:cfRule type="expression" dxfId="22" priority="17">
+      <x:formula>F16="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="23" priority="18">
+      <x:formula>F16="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F17:F17">
+    <x:cfRule type="expression" dxfId="24" priority="19">
+      <x:formula>F17="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="25" priority="20">
+      <x:formula>F17="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F18:F18">
+    <x:cfRule type="expression" dxfId="26" priority="21">
+      <x:formula>F18="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="27" priority="22">
+      <x:formula>F18="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F20:F20">
+    <x:cfRule type="expression" dxfId="28" priority="23">
+      <x:formula>F20="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="29" priority="24">
+      <x:formula>F20="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F21:F21">
+    <x:cfRule type="expression" dxfId="30" priority="25">
+      <x:formula>F21="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="31" priority="26">
+      <x:formula>F21="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F22:F22">
+    <x:cfRule type="expression" dxfId="32" priority="27">
+      <x:formula>F22="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="33" priority="28">
+      <x:formula>F22="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F23:F23">
+    <x:cfRule type="expression" dxfId="34" priority="29">
+      <x:formula>F23="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="35" priority="30">
+      <x:formula>F23="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G6:G6">
+    <x:cfRule type="expression" dxfId="36" priority="31">
+      <x:formula>G6="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="37" priority="32">
+      <x:formula>G6="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G7:G7">
+    <x:cfRule type="expression" dxfId="38" priority="33">
+      <x:formula>G7="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="39" priority="34">
+      <x:formula>G7="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G8:G8">
+    <x:cfRule type="expression" dxfId="40" priority="35">
+      <x:formula>G8="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="41" priority="36">
+      <x:formula>G8="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G10:G10">
+    <x:cfRule type="expression" dxfId="42" priority="37">
+      <x:formula>G10="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="43" priority="38">
+      <x:formula>G10="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G11:G11">
+    <x:cfRule type="expression" dxfId="44" priority="39">
+      <x:formula>G11="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="45" priority="40">
+      <x:formula>G11="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G12:G12">
+    <x:cfRule type="expression" dxfId="46" priority="41">
+      <x:formula>G12="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="47" priority="42">
+      <x:formula>G12="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G13:G13">
+    <x:cfRule type="expression" dxfId="48" priority="43">
+      <x:formula>G13="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="49" priority="44">
+      <x:formula>G13="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G14:G14">
+    <x:cfRule type="expression" dxfId="50" priority="45">
+      <x:formula>G14="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="51" priority="46">
+      <x:formula>G14="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G16:G16">
+    <x:cfRule type="expression" dxfId="52" priority="47">
+      <x:formula>G16="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="53" priority="48">
+      <x:formula>G16="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G17:G17">
+    <x:cfRule type="expression" dxfId="54" priority="49">
+      <x:formula>G17="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="55" priority="50">
+      <x:formula>G17="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G18:G18">
+    <x:cfRule type="expression" dxfId="56" priority="51">
+      <x:formula>G18="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="57" priority="52">
+      <x:formula>G18="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G20:G20">
+    <x:cfRule type="expression" dxfId="58" priority="53">
+      <x:formula>G20="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="59" priority="54">
+      <x:formula>G20="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G21:G21">
+    <x:cfRule type="expression" dxfId="60" priority="55">
+      <x:formula>G21="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="61" priority="56">
+      <x:formula>G21="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G22:G22">
+    <x:cfRule type="expression" dxfId="62" priority="57">
+      <x:formula>G22="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="63" priority="58">
+      <x:formula>G22="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G23:G23">
+    <x:cfRule type="expression" dxfId="64" priority="59">
+      <x:formula>G23="Correct"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="65" priority="60">
+      <x:formula>G23="Check"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2486,7 +3862,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2955,7 +4331,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3363,7 +4739,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3396,44 +4772,44 @@
         <x:v>Required action</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="30" customHeight="1">
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="230" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="70" t="str">
-        <x:v>In class: complete Class Practice alongside slides 7–12.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
+        <x:v>In class: calculate the five ratios on Class Practice and review DuPont.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="230" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="70" t="str">
-        <x:v>After class: compare the two fictional retailers using supplied Company Data.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+        <x:v>In class: complete all eight CORE ratios for both retailers, the expense test, and dashboard review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="230" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="70" t="str">
-        <x:v>Complete the eight CORE ratio rows for both firms; remaining rows are optional.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>In class: reconcile DuPont ROE, predict the expense change, then run the test in B20.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="230" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="70" t="str">
-        <x:v>Use DuPont and the operating-expense test to identify the performance driver.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>In class: compare the linked Ratio Dashboard and identify evidence for a recommendation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="231" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="73" t="str">
-        <x:v>Use the linked dashboard and checks to defend the recommendation.</x:v>
+        <x:v>After class: finish Class Practice A21, DuPont &amp; Driver B29, and Checks &amp; Recommendation A19. Review checks and submit one workbook to Canvas.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
@@ -3581,419 +4957,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="3" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="243" t="str">
-        <x:v>M04 | Class Practice — same example as the slides</x:v>
-      </x:c>
-      <x:c r="B1" s="243"/>
-      <x:c r="C1" s="243"/>
-      <x:c r="D1" s="243"/>
-      <x:c r="E1" s="243"/>
-      <x:c r="F1" s="243"/>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="244" t="str">
-        <x:v>Slides 7–12: enter five formulas in E5:E9, then explain the DuPont drivers. Return here for the in-class brief.</x:v>
-      </x:c>
-      <x:c r="B2" s="241"/>
-      <x:c r="C2" s="241"/>
-      <x:c r="D2" s="241"/>
-      <x:c r="E2" s="241"/>
-      <x:c r="F2" s="241"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="241"/>
-      <x:c r="B3" s="241"/>
-      <x:c r="C3" s="241"/>
-      <x:c r="D3" s="241"/>
-      <x:c r="E3" s="241"/>
-      <x:c r="F3" s="241"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="255" t="str">
-        <x:v>Given inputs (USD)</x:v>
-      </x:c>
-      <x:c r="B4" s="255" t="str">
-        <x:v>Amount</x:v>
-      </x:c>
-      <x:c r="C4" s="241"/>
-      <x:c r="D4" s="255" t="str">
-        <x:v>Five core signals</x:v>
-      </x:c>
-      <x:c r="E4" s="255" t="str">
-        <x:v>Your formula</x:v>
-      </x:c>
-      <x:c r="F4" s="255" t="str">
-        <x:v>Definition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="241" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="B5" s="247" t="n">
-        <x:v>120000</x:v>
-      </x:c>
-      <x:c r="C5" s="241"/>
-      <x:c r="D5" s="241" t="str">
-        <x:v>Current ratio</x:v>
-      </x:c>
-      <x:c r="E5" s="249"/>
-      <x:c r="F5" s="244" t="str">
-        <x:v>Current assets / current liabilities</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="241" t="str">
-        <x:v>Cost of goods sold</x:v>
-      </x:c>
-      <x:c r="B6" s="247" t="n">
-        <x:v>48000</x:v>
-      </x:c>
-      <x:c r="C6" s="241"/>
-      <x:c r="D6" s="241" t="str">
-        <x:v>Gross margin</x:v>
-      </x:c>
-      <x:c r="E6" s="250"/>
-      <x:c r="F6" s="244" t="str">
-        <x:v>(Revenue - COGS) / revenue</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="241" t="str">
-        <x:v>Net income</x:v>
-      </x:c>
-      <x:c r="B7" s="247" t="n">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="C7" s="241"/>
-      <x:c r="D7" s="241" t="str">
-        <x:v>Asset turnover</x:v>
-      </x:c>
-      <x:c r="E7" s="249"/>
-      <x:c r="F7" s="244" t="str">
-        <x:v>Revenue / average assets</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="241" t="str">
-        <x:v>Average assets</x:v>
-      </x:c>
-      <x:c r="B8" s="247" t="n">
-        <x:v>80000</x:v>
-      </x:c>
-      <x:c r="C8" s="241"/>
-      <x:c r="D8" s="241" t="str">
-        <x:v>Debt ratio</x:v>
-      </x:c>
-      <x:c r="E8" s="250"/>
-      <x:c r="F8" s="244" t="str">
-        <x:v>Total debt / ending assets</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="241" t="str">
-        <x:v>Current assets</x:v>
-      </x:c>
-      <x:c r="B9" s="247" t="n">
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="C9" s="241"/>
-      <x:c r="D9" s="241" t="str">
-        <x:v>ROE</x:v>
-      </x:c>
-      <x:c r="E9" s="250"/>
-      <x:c r="F9" s="244" t="str">
-        <x:v>Net income / average equity</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="241" t="str">
-        <x:v>Current liabilities</x:v>
-      </x:c>
-      <x:c r="B10" s="247" t="n">
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="C10" s="241"/>
-      <x:c r="D10" s="241"/>
-      <x:c r="E10" s="241"/>
-      <x:c r="F10" s="244"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="241" t="str">
-        <x:v>Total debt</x:v>
-      </x:c>
-      <x:c r="B11" s="247" t="n">
-        <x:v>44000</x:v>
-      </x:c>
-      <x:c r="C11" s="241"/>
-      <x:c r="D11" s="241"/>
-      <x:c r="E11" s="241"/>
-      <x:c r="F11" s="244"/>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="241" t="str">
-        <x:v>Ending assets</x:v>
-      </x:c>
-      <x:c r="B12" s="247" t="n">
-        <x:v>88000</x:v>
-      </x:c>
-      <x:c r="C12" s="241"/>
-      <x:c r="D12" s="255" t="str">
-        <x:v>DuPont bridge</x:v>
-      </x:c>
-      <x:c r="E12" s="255" t="str">
-        <x:v>Linked result</x:v>
-      </x:c>
-      <x:c r="F12" s="256" t="str">
-        <x:v>Meaning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="241" t="str">
-        <x:v>Beginning equity</x:v>
-      </x:c>
-      <x:c r="B13" s="247" t="n">
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="C13" s="241"/>
-      <x:c r="D13" s="241" t="str">
-        <x:v>Net margin</x:v>
-      </x:c>
-      <x:c r="E13" s="251" t="n">
-        <x:f>B7/B5</x:f>
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F13" s="244" t="str">
-        <x:v>After all expenses; compare with gross margin</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="241" t="str">
-        <x:v>Ending equity</x:v>
-      </x:c>
-      <x:c r="B14" s="247" t="n">
-        <x:v>32000</x:v>
-      </x:c>
-      <x:c r="C14" s="241"/>
-      <x:c r="D14" s="241" t="str">
-        <x:v>Asset turnover</x:v>
-      </x:c>
-      <x:c r="E14" s="252" t="str">
-        <x:f>IF(E7="","",E7)</x:f>
-      </x:c>
-      <x:c r="F14" s="244" t="str">
-        <x:v>Same ratio as E7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="241"/>
-      <x:c r="B15" s="241"/>
-      <x:c r="C15" s="241"/>
-      <x:c r="D15" s="241" t="str">
-        <x:v>Equity multiplier</x:v>
-      </x:c>
-      <x:c r="E15" s="252" t="n">
-        <x:f>B8/AVERAGE(B13:B14)</x:f>
-        <x:v>2.6666666666666665</x:v>
-      </x:c>
-      <x:c r="F15" s="244" t="str">
-        <x:v>Use the full value; display rounds to 2.67x</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="241"/>
-      <x:c r="B16" s="241"/>
-      <x:c r="C16" s="241"/>
-      <x:c r="D16" s="241" t="str">
-        <x:v>DuPont ROE</x:v>
-      </x:c>
-      <x:c r="E16" s="251" t="str">
-        <x:f>IF(E14="","",E13*E14*E15)</x:f>
-      </x:c>
-      <x:c r="F16" s="244" t="str">
-        <x:v>Net margin x turnover x equity multiplier</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="241"/>
-      <x:c r="B17" s="241"/>
-      <x:c r="C17" s="241"/>
-      <x:c r="D17" s="241" t="str">
-        <x:v>Reconciliation difference</x:v>
-      </x:c>
-      <x:c r="E17" s="251" t="str">
-        <x:f>IF(OR(E9="",E16=""),"",E16-E9)</x:f>
-      </x:c>
-      <x:c r="F17" s="244" t="str">
-        <x:v>Should be zero when ROE is consistent</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="241"/>
-      <x:c r="B18" s="241"/>
-      <x:c r="C18" s="241"/>
-      <x:c r="D18" s="241"/>
-      <x:c r="E18" s="241"/>
-      <x:c r="F18" s="241"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="241"/>
-      <x:c r="B19" s="241"/>
-      <x:c r="C19" s="241"/>
-      <x:c r="D19" s="241"/>
-      <x:c r="E19" s="241"/>
-      <x:c r="F19" s="241"/>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="241" t="str">
-        <x:v>In-class brief: two sentences using two ratios, a driver, a risk, and a follow-up data request.</x:v>
-      </x:c>
-      <x:c r="B20" s="241"/>
-      <x:c r="C20" s="241"/>
-      <x:c r="D20" s="241"/>
-      <x:c r="E20" s="241"/>
-      <x:c r="F20" s="241"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="254"/>
-      <x:c r="B21" s="254"/>
-      <x:c r="C21" s="254"/>
-      <x:c r="D21" s="254"/>
-      <x:c r="E21" s="254"/>
-      <x:c r="F21" s="254"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="254"/>
-      <x:c r="B22" s="254"/>
-      <x:c r="C22" s="254"/>
-      <x:c r="D22" s="254"/>
-      <x:c r="E22" s="254"/>
-      <x:c r="F22" s="254"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="254"/>
-      <x:c r="B23" s="254"/>
-      <x:c r="C23" s="254"/>
-      <x:c r="D23" s="254"/>
-      <x:c r="E23" s="254"/>
-      <x:c r="F23" s="254"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="254"/>
-      <x:c r="B24" s="254"/>
-      <x:c r="C24" s="254"/>
-      <x:c r="D24" s="254"/>
-      <x:c r="E24" s="254"/>
-      <x:c r="F24" s="254"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="241"/>
-      <x:c r="B25" s="241"/>
-      <x:c r="C25" s="241"/>
-      <x:c r="D25" s="241"/>
-      <x:c r="E25" s="241"/>
-      <x:c r="F25" s="241"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="241"/>
-      <x:c r="B26" s="241"/>
-      <x:c r="C26" s="241"/>
-      <x:c r="D26" s="241"/>
-      <x:c r="E26" s="241"/>
-      <x:c r="F26" s="241"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="244" t="str">
-        <x:v>After class: move to Company Data and Student Calculations. The two-retailer case uses different data deliberately. Complete CORE rows 6, 10, 12, 14, 17, 18, 22, and 23; optional rows may stay blank.</x:v>
-      </x:c>
-      <x:c r="B27" s="241"/>
-      <x:c r="C27" s="241"/>
-      <x:c r="D27" s="241"/>
-      <x:c r="E27" s="241"/>
-      <x:c r="F27" s="241"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="241"/>
-      <x:c r="B28" s="241"/>
-      <x:c r="C28" s="241"/>
-      <x:c r="D28" s="241"/>
-      <x:c r="E28" s="241"/>
-      <x:c r="F28" s="241"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="241"/>
-      <x:c r="B29" s="241"/>
-      <x:c r="C29" s="241"/>
-      <x:c r="D29" s="241"/>
-      <x:c r="E29" s="241"/>
-      <x:c r="F29" s="241"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="244" t="str">
-        <x:v>Source: instructor-created classroom example matching the M04 slides. No external retrieval required.</x:v>
-      </x:c>
-      <x:c r="B30" s="241"/>
-      <x:c r="C30" s="241"/>
-      <x:c r="D30" s="241"/>
-      <x:c r="E30" s="241"/>
-      <x:c r="F30" s="241"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="241"/>
-      <x:c r="B31" s="241"/>
-      <x:c r="C31" s="241"/>
-      <x:c r="D31" s="241"/>
-      <x:c r="E31" s="241"/>
-      <x:c r="F31" s="241"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="241"/>
-      <x:c r="B32" s="241"/>
-      <x:c r="C32" s="241"/>
-      <x:c r="D32" s="241"/>
-      <x:c r="E32" s="241"/>
-      <x:c r="F32" s="241"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="241"/>
-      <x:c r="B33" s="241"/>
-      <x:c r="C33" s="241"/>
-      <x:c r="D33" s="241"/>
-      <x:c r="E33" s="241"/>
-      <x:c r="F33" s="241"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="241"/>
-      <x:c r="B34" s="241"/>
-      <x:c r="C34" s="241"/>
-      <x:c r="D34" s="241"/>
-      <x:c r="E34" s="241"/>
-      <x:c r="F34" s="241"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A20:F20"/>
-    <x:mergeCell ref="A21:F24"/>
-    <x:mergeCell ref="A27:F28"/>
-    <x:mergeCell ref="A30:F31"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>